--- a/files/九龙-何文田-芳菲.xlsx
+++ b/files/九龙-何文田-芳菲.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="芳菲 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -808,7 +669,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1958,7 +1819,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2004,7 +1865,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2234,7 +2095,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2280,7 +2141,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2372,7 +2233,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2418,7 +2279,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2510,7 +2371,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2648,7 +2509,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2786,7 +2647,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2832,7 +2693,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2924,7 +2785,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2970,7 +2831,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3016,7 +2877,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3062,7 +2923,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3108,7 +2969,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3154,7 +3015,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3200,7 +3061,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3246,7 +3107,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3292,7 +3153,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3338,7 +3199,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3384,7 +3245,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3430,7 +3291,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3476,7 +3337,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3568,7 +3429,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3614,7 +3475,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3660,7 +3521,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3706,7 +3567,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3752,7 +3613,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3798,7 +3659,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3894,7 +3755,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3966,858 +3827,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>芳菲 - 芳菲 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>71 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>17 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>31 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 742呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 417呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,638万
-$35,230/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$1,052万
-$36,797/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 414呎 (1房)
-$1,186万
-$28,643/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,607万
-$34,563/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$1,033万
-$36,119/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,390万
-$33,563/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,646万
-$34,229/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$991万
-$34,654/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,376万
-$33,237/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,631万
-$33,902/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$982万
-$34,322/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,363万
-$32,915/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,535万
-$33,013/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$972万
-$33,993/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,349万
-$32,594/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,520万
-$32,692/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$963万
-$33,668/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,336万
-$32,280/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,506万
-$32,376/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$954万
-$33,350/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,323万
-$31,964/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,542万
-$32,058/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$945万
-$33,031/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,310万
-$31,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,184万
-$24,605/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$708万
-$24,752/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,298万
-$31,345/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,462万
-$31,439/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$910万
-$31,836/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,285万
-$31,043/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,247万
-$26,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$777万
-$27,164/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,260万
-$30,444/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,278万
-$27,482/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$769万
-$26,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,248万
-$30,147/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,455万
-$30,241/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$679万
-$23,731/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,236万
-$29,855/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,440万
-$29,946/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$763万
-$26,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,224万
-$29,570/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,241万
-$26,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$756万
-$26,427/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,212万
-$29,280/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,202万
-$25,841/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$782万
-$27,357/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,200万
-$28,998/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,177万
-$25,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$741万
-$25,916/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,046万
-$25,271/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,154万
-$24,002/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$734万
-$25,661/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$912万
-$22,039/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 481呎 (2房)
-$1,172万
-$24,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$720万
-$25,171/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$1,016万
-$24,546/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,301万
-$27,976/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$689万
-$24,077/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$997万
-$24,082/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$1,073万
-$23,069/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$738万
-$25,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$852万
-$20,592/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-$968万
-$20,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$723万
-$25,283/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 414呎 (2房)
-$971万
-$23,447/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 465呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$597万
-$20,885/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 377呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-芳菲.xlsx
+++ b/files/九龙-何文田-芳菲.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="芳菲" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3827,4 +4015,858 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>芳菲 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 742呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 417呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1638万
+$35,230/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$1052万
+$36,797/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 414呎 (1房)
+$1186万
+$28,643/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1607万
+$34,563/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$1033万
+$36,119/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1390万
+$33,563/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1646万
+$34,229/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$991万
+$34,654/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1376万
+$33,237/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1631万
+$33,902/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$982万
+$34,322/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1363万
+$32,915/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1535万
+$33,013/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$972万
+$33,993/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1349万
+$32,594/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1520万
+$32,692/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$963万
+$33,668/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1336万
+$32,280/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1506万
+$32,376/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$954万
+$33,350/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1323万
+$31,964/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1542万
+$32,058/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$945万
+$33,031/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1310万
+$31,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1184万
+$24,605/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$708万
+$24,752/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1298万
+$31,345/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1462万
+$31,439/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$910万
+$31,836/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1285万
+$31,043/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1247万
+$26,826/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$777万
+$27,164/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1260万
+$30,444/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1278万
+$27,482/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$769万
+$26,902/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1248万
+$30,147/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1455万
+$30,241/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$679万
+$23,731/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1236万
+$29,855/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1440万
+$29,946/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$763万
+$26,685/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1224万
+$29,570/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1241万
+$26,692/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$756万
+$26,427/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1212万
+$29,280/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1202万
+$25,841/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$782万
+$27,357/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1200万
+$28,998/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1177万
+$25,305/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$741万
+$25,916/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1046万
+$25,271/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1154万
+$24,002/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$734万
+$25,661/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$912万
+$22,039/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 481呎 (2房)
+$1172万
+$24,360/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$720万
+$25,171/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$1016万
+$24,546/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1301万
+$27,976/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$689万
+$24,077/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$997万
+$24,082/呎
+(22年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$1073万
+$23,069/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$738万
+$25,808/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$852万
+$20,592/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+$968万
+$20,826/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$723万
+$25,283/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 414呎 (2房)
+$971万
+$23,447/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 465呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$597万
+$20,885/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 377呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-芳菲.xlsx
+++ b/files/九龙-何文田-芳菲.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3888,27 +3888,23 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>10782200</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>28600</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4075,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4089,7 +4085,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4853,12 +4849,12 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 377呎 (2房)
-招标单位
--
-(在售)</t>
+$1078万
+$28,600/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-芳菲.xlsx
+++ b/files/九龙-何文田-芳菲.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -722,6 +726,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -772,6 +796,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -822,6 +866,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -868,6 +932,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>11858000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>28643</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -914,6 +994,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8050860</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>28150</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -960,6 +1056,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>12532230</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>26951</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1006,6 +1118,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>10629675</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>25676</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1052,6 +1180,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7902450</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>27631</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1098,6 +1242,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>12295080</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>26441</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1144,6 +1304,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>10526400</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>25426</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1190,6 +1366,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7581915</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>26510</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1236,6 +1428,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>12594960</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>26185</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1282,6 +1490,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>10424655</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>25180</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1328,6 +1552,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7509240</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>26256</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1374,6 +1614,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>12474855</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>25935</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1420,6 +1676,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>10322910</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>24935</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1466,6 +1738,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7437330</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>26005</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1512,6 +1800,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>11743515</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>25255</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1558,6 +1862,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>10223460</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>24694</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1604,6 +1924,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>7366185</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>25756</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1650,6 +1986,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>11629530</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>25010</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1696,6 +2048,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>10123245</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>24452</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1742,6 +2110,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>7296570</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>25512</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1788,6 +2172,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>11517075</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>24768</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1834,6 +2234,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>10023795</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>24212</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1880,6 +2296,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>7226955</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>25269</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1926,6 +2358,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>11796300</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>24525</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1972,6 +2420,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>9927405</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>23979</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2018,6 +2482,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>7079000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>24752</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2064,6 +2544,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>11835000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>24605</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2110,6 +2606,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>9831780</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>23748</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2156,6 +2668,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>6965325</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>24354</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2202,6 +2730,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>11183535</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>24051</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2248,6 +2792,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>9642060</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>23290</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2294,6 +2854,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>7769000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>27164</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2340,6 +2916,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>12474000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>26826</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2386,6 +2978,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>9547965</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>23063</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2432,6 +3040,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>7694000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>26902</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2478,6 +3102,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>12779000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>27482</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2524,6 +3164,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>9455400</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>22839</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2570,6 +3226,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>6787000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>23731</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2616,6 +3288,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>11127690</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>23134</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2662,6 +3350,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>9365130</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>22621</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2708,6 +3412,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>7632000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>26685</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2754,6 +3474,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>11019060</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>22909</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2800,6 +3536,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>9273330</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>22399</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2846,6 +3598,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>7558000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>26427</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2892,6 +3660,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>12412000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>26692</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2938,6 +3722,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>9183825</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>22183</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2984,6 +3784,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>7824000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>27357</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3030,6 +3846,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>12016000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>25841</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3076,6 +3908,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>10462000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>25271</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3122,6 +3970,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>7412000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>25916</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3168,6 +4032,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>11767000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>25305</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3214,6 +4094,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>9124000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>22039</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3260,6 +4156,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>7339000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>25661</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3306,6 +4218,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>11545000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>24002</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3352,6 +4280,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>10162000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>24546</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3398,6 +4342,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>7199000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>25171</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3444,6 +4404,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>11717000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>24360</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3490,6 +4466,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>9970000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>24082</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3536,6 +4528,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>6886000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>24077</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3582,6 +4590,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>9951885</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21402</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3628,6 +4652,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>8525000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>20592</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3674,6 +4714,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>7381000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>25808</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3720,6 +4776,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>10727000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>23069</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3766,6 +4838,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>9707000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>23447</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3812,6 +4900,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>7231000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>25283</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3858,6 +4962,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>9684000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>20826</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3904,6 +5024,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>10782200</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>28600</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3950,6 +5086,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>5973000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>20885</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4000,13 +5152,33 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4172,7 +5344,7 @@
           <t>C | 414呎 (1房)
 $1186万
 $28,643/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -4404,7 +5576,7 @@
           <t>A | 481呎 (2房)
 $1184万
 $24,605/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -4412,7 +5584,7 @@
           <t>B | 286呎 (1房)
 $708万
 $24,752/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -4466,7 +5638,7 @@
           <t>A | 465呎 (2房)
 $1247万
 $26,826/呎
-(23年-01月)</t>
+(23年-01月-12日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -4474,7 +5646,7 @@
           <t>B | 286呎 (1房)
 $777万
 $27,164/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -4497,7 +5669,7 @@
           <t>A | 465呎 (2房)
 $1278万
 $27,482/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -4505,7 +5677,7 @@
           <t>B | 286呎 (1房)
 $769万
 $26,902/呎
-(23年-03月)</t>
+(23年-03月-22日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -4536,7 +5708,7 @@
           <t>B | 286呎 (1房)
 $679万
 $23,731/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -4567,7 +5739,7 @@
           <t>B | 286呎 (1房)
 $763万
 $26,685/呎
-(22年-12月)</t>
+(22年-12月-19日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -4590,7 +5762,7 @@
           <t>A | 465呎 (2房)
 $1241万
 $26,692/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -4598,7 +5770,7 @@
           <t>B | 286呎 (1房)
 $756万
 $26,427/呎
-(23年-01月)</t>
+(23年-01月-03日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -4621,7 +5793,7 @@
           <t>A | 465呎 (2房)
 $1202万
 $25,841/呎
-(23年-01月)</t>
+(23年-01月-09日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -4629,7 +5801,7 @@
           <t>B | 286呎 (1房)
 $782万
 $27,357/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -4652,7 +5824,7 @@
           <t>A | 465呎 (2房)
 $1177万
 $25,305/呎
-(23年-05月)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -4660,7 +5832,7 @@
           <t>B | 286呎 (1房)
 $741万
 $25,916/呎
-(23年-01月)</t>
+(23年-01月-03日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -4668,7 +5840,7 @@
           <t>C | 414呎 (2房)
 $1046万
 $25,271/呎
-(22年-12月)</t>
+(22年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -4683,7 +5855,7 @@
           <t>A | 481呎 (2房)
 $1154万
 $24,002/呎
-(23年-05月)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -4691,7 +5863,7 @@
           <t>B | 286呎 (1房)
 $734万
 $25,661/呎
-(22年-12月)</t>
+(22年-12月-19日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -4699,7 +5871,7 @@
           <t>C | 414呎 (2房)
 $912万
 $22,039/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -4714,7 +5886,7 @@
           <t>A | 481呎 (2房)
 $1172万
 $24,360/呎
-(23年-04月)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -4722,7 +5894,7 @@
           <t>B | 286呎 (1房)
 $720万
 $25,171/呎
-(22年-10月)</t>
+(22年-10月-02日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -4730,7 +5902,7 @@
           <t>C | 414呎 (2房)
 $1016万
 $24,546/呎
-(23年-04月)</t>
+(23年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -4753,7 +5925,7 @@
           <t>B | 286呎 (1房)
 $689万
 $24,077/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -4761,7 +5933,7 @@
           <t>C | 414呎 (2房)
 $997万
 $24,082/呎
-(22年-09月)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -4776,7 +5948,7 @@
           <t>A | 465呎 (2房)
 $1073万
 $23,069/呎
-(23年-01月)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -4784,7 +5956,7 @@
           <t>B | 286呎 (1房)
 $738万
 $25,808/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -4792,7 +5964,7 @@
           <t>C | 414呎 (2房)
 $852万
 $20,592/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -4807,7 +5979,7 @@
           <t>A | 465呎 (2房)
 $968万
 $20,826/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -4815,7 +5987,7 @@
           <t>B | 286呎 (1房)
 $723万
 $25,283/呎
-(21年-08月)</t>
+(21年-08月-23日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -4823,7 +5995,7 @@
           <t>C | 414呎 (2房)
 $971万
 $23,447/呎
-(21年-08月)</t>
+(21年-08月-24日)</t>
         </is>
       </c>
     </row>
@@ -4846,7 +6018,7 @@
           <t>B | 286呎 (1房)
 $597万
 $20,885/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -4854,7 +6026,7 @@
           <t>C | 377呎 (2房)
 $1078万
 $28,600/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-芳菲.xlsx
+++ b/files/九龙-何文田-芳菲.xlsx
@@ -994,14 +994,14 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>8050860</v>
+        <v>8103480</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>28150</v>
+        <v>28334</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1056,14 +1056,14 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>12532230</v>
+        <v>12614140</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>26951</v>
+        <v>27127</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1118,14 +1118,14 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>10629675</v>
+        <v>10699150</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>25676</v>
+        <v>25843</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1180,14 +1180,14 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>7902450</v>
+        <v>7954100</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>27631</v>
+        <v>27812</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1242,14 +1242,14 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>12295080</v>
+        <v>12375440</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26441</v>
+        <v>26614</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1304,14 +1304,14 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>10526400</v>
+        <v>10595200</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>25426</v>
+        <v>25592</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1366,14 +1366,14 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>7581915</v>
+        <v>7631470</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>26510</v>
+        <v>26683</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>12594960</v>
+        <v>12677280</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>26185</v>
+        <v>26356</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1490,14 +1490,14 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>10424655</v>
+        <v>10492790</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>25180</v>
+        <v>25345</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1552,14 +1552,14 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>7509240</v>
+        <v>7558320</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>26256</v>
+        <v>26428</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>12474855</v>
+        <v>12556390</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>25935</v>
+        <v>26105</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1676,14 +1676,14 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>10322910</v>
+        <v>10390380</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>24935</v>
+        <v>25098</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1738,14 +1738,14 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>7437330</v>
+        <v>7485940</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>26005</v>
+        <v>26175</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1800,14 +1800,14 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>11743515</v>
+        <v>11820270</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>25255</v>
+        <v>25420</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1862,14 +1862,14 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>10223460</v>
+        <v>10290280</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>24694</v>
+        <v>24856</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1924,14 +1924,14 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>7366185</v>
+        <v>7414330</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>25756</v>
+        <v>25924</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -1986,14 +1986,14 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>11629530</v>
+        <v>11705540</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>25010</v>
+        <v>25173</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2048,14 +2048,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>10123245</v>
+        <v>10189410</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>24452</v>
+        <v>24612</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>7296570</v>
+        <v>7344260</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>25512</v>
+        <v>25679</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2172,14 +2172,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>11517075</v>
+        <v>11592350</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>24768</v>
+        <v>24930</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>10023795</v>
+        <v>10089310</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>24212</v>
+        <v>24370</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>7226955</v>
+        <v>7274190</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>25269</v>
+        <v>25434</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2358,14 +2358,14 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>11796300</v>
+        <v>11873400</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>24525</v>
+        <v>24685</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2420,14 +2420,14 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>9927405</v>
+        <v>9992290</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>23979</v>
+        <v>24136</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2606,14 +2606,14 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>9831780</v>
+        <v>9896040</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>23748</v>
+        <v>23903</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2668,14 +2668,14 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>6965325</v>
+        <v>7010850</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>24354</v>
+        <v>24513</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2730,14 +2730,14 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>11183535</v>
+        <v>11256630</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>24051</v>
+        <v>24208</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2792,14 +2792,14 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>9642060</v>
+        <v>9705080</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>23290</v>
+        <v>23442</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>9547965</v>
+        <v>9610370</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>23063</v>
+        <v>23213</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3164,14 +3164,14 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>9455400</v>
+        <v>9517200</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>22839</v>
+        <v>22988</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3288,14 +3288,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>11127690</v>
+        <v>11200420</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>23134</v>
+        <v>23286</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3350,14 +3350,14 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>9365130</v>
+        <v>9426340</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>22621</v>
+        <v>22769</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3474,14 +3474,14 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>11019060</v>
+        <v>11091080</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>22909</v>
+        <v>23058</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3536,14 +3536,14 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>9273330</v>
+        <v>9333940</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>22399</v>
+        <v>22546</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>9183825</v>
+        <v>9243850</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>22183</v>
+        <v>22328</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -4590,14 +4590,14 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>9951885</v>
+        <v>10016930</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>21402</v>
+        <v>21542</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>

--- a/files/九龙-何文田-芳菲.xlsx
+++ b/files/九龙-何文田-芳菲.xlsx
@@ -5344,7 +5344,7 @@
           <t>C | 414呎 (1房)
 $1186万
 $28,643/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
           <t>A | 481呎 (2房)
 $1184万
 $24,605/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -5584,7 +5584,7 @@
           <t>B | 286呎 (1房)
 $708万
 $24,752/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -5638,7 +5638,7 @@
           <t>A | 465呎 (2房)
 $1247万
 $26,826/呎
-(23年-01月-12日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -5646,7 +5646,7 @@
           <t>B | 286呎 (1房)
 $777万
 $27,164/呎
-(22年-09月-25日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -5669,7 +5669,7 @@
           <t>A | 465呎 (2房)
 $1278万
 $27,482/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -5677,7 +5677,7 @@
           <t>B | 286呎 (1房)
 $769万
 $26,902/呎
-(23年-03月-22日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -5708,7 +5708,7 @@
           <t>B | 286呎 (1房)
 $679万
 $23,731/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -5739,7 +5739,7 @@
           <t>B | 286呎 (1房)
 $763万
 $26,685/呎
-(22年-12月-19日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -5762,7 +5762,7 @@
           <t>A | 465呎 (2房)
 $1241万
 $26,692/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -5770,7 +5770,7 @@
           <t>B | 286呎 (1房)
 $756万
 $26,427/呎
-(23年-01月-03日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -5793,7 +5793,7 @@
           <t>A | 465呎 (2房)
 $1202万
 $25,841/呎
-(23年-01月-09日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -5801,7 +5801,7 @@
           <t>B | 286呎 (1房)
 $782万
 $27,357/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -5824,7 +5824,7 @@
           <t>A | 465呎 (2房)
 $1177万
 $25,305/呎
-(23年-05月-02日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -5832,7 +5832,7 @@
           <t>B | 286呎 (1房)
 $741万
 $25,916/呎
-(23年-01月-03日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -5840,7 +5840,7 @@
           <t>C | 414呎 (2房)
 $1046万
 $25,271/呎
-(22年-12月-04日)</t>
+(22年-12月)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
           <t>A | 481呎 (2房)
 $1154万
 $24,002/呎
-(23年-05月-29日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -5863,7 +5863,7 @@
           <t>B | 286呎 (1房)
 $734万
 $25,661/呎
-(22年-12月-19日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -5871,7 +5871,7 @@
           <t>C | 414呎 (2房)
 $912万
 $22,039/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
           <t>A | 481呎 (2房)
 $1172万
 $24,360/呎
-(23年-04月-26日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -5894,7 +5894,7 @@
           <t>B | 286呎 (1房)
 $720万
 $25,171/呎
-(22年-10月-02日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -5902,7 +5902,7 @@
           <t>C | 414呎 (2房)
 $1016万
 $24,546/呎
-(23年-04月-12日)</t>
+(23年-04月)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
           <t>B | 286呎 (1房)
 $689万
 $24,077/呎
-(22年-10月-04日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -5933,7 +5933,7 @@
           <t>C | 414呎 (2房)
 $997万
 $24,082/呎
-(22年-09月-26日)</t>
+(22年-09月)</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
           <t>A | 465呎 (2房)
 $1073万
 $23,069/呎
-(23年-01月-31日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -5956,7 +5956,7 @@
           <t>B | 286呎 (1房)
 $738万
 $25,808/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -5964,7 +5964,7 @@
           <t>C | 414呎 (2房)
 $852万
 $20,592/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
           <t>A | 465呎 (2房)
 $968万
 $20,826/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -5987,7 +5987,7 @@
           <t>B | 286呎 (1房)
 $723万
 $25,283/呎
-(21年-08月-23日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -5995,7 +5995,7 @@
           <t>C | 414呎 (2房)
 $971万
 $23,447/呎
-(21年-08月-24日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
           <t>B | 286呎 (1房)
 $597万
 $20,885/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -6026,7 +6026,7 @@
           <t>C | 377呎 (2房)
 $1078万
 $28,600/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-芳菲.xlsx
+++ b/files/九龙-何文田-芳菲.xlsx
@@ -5344,7 +5344,7 @@
           <t>C | 414呎 (1房)
 $1186万
 $28,643/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
           <t>A | 481呎 (2房)
 $1184万
 $24,605/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -5584,7 +5584,7 @@
           <t>B | 286呎 (1房)
 $708万
 $24,752/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -5638,7 +5638,7 @@
           <t>A | 465呎 (2房)
 $1247万
 $26,826/呎
-(23年-01月)</t>
+(23年-01月-12日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -5646,7 +5646,7 @@
           <t>B | 286呎 (1房)
 $777万
 $27,164/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -5669,7 +5669,7 @@
           <t>A | 465呎 (2房)
 $1278万
 $27,482/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -5677,7 +5677,7 @@
           <t>B | 286呎 (1房)
 $769万
 $26,902/呎
-(23年-03月)</t>
+(23年-03月-22日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -5708,7 +5708,7 @@
           <t>B | 286呎 (1房)
 $679万
 $23,731/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -5739,7 +5739,7 @@
           <t>B | 286呎 (1房)
 $763万
 $26,685/呎
-(22年-12月)</t>
+(22年-12月-19日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -5762,7 +5762,7 @@
           <t>A | 465呎 (2房)
 $1241万
 $26,692/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -5770,7 +5770,7 @@
           <t>B | 286呎 (1房)
 $756万
 $26,427/呎
-(23年-01月)</t>
+(23年-01月-03日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -5793,7 +5793,7 @@
           <t>A | 465呎 (2房)
 $1202万
 $25,841/呎
-(23年-01月)</t>
+(23年-01月-09日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -5801,7 +5801,7 @@
           <t>B | 286呎 (1房)
 $782万
 $27,357/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -5824,7 +5824,7 @@
           <t>A | 465呎 (2房)
 $1177万
 $25,305/呎
-(23年-05月)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -5832,7 +5832,7 @@
           <t>B | 286呎 (1房)
 $741万
 $25,916/呎
-(23年-01月)</t>
+(23年-01月-03日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -5840,7 +5840,7 @@
           <t>C | 414呎 (2房)
 $1046万
 $25,271/呎
-(22年-12月)</t>
+(22年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
           <t>A | 481呎 (2房)
 $1154万
 $24,002/呎
-(23年-05月)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -5863,7 +5863,7 @@
           <t>B | 286呎 (1房)
 $734万
 $25,661/呎
-(22年-12月)</t>
+(22年-12月-19日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -5871,7 +5871,7 @@
           <t>C | 414呎 (2房)
 $912万
 $22,039/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
           <t>A | 481呎 (2房)
 $1172万
 $24,360/呎
-(23年-04月)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -5894,7 +5894,7 @@
           <t>B | 286呎 (1房)
 $720万
 $25,171/呎
-(22年-10月)</t>
+(22年-10月-02日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -5902,7 +5902,7 @@
           <t>C | 414呎 (2房)
 $1016万
 $24,546/呎
-(23年-04月)</t>
+(23年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
           <t>B | 286呎 (1房)
 $689万
 $24,077/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -5933,7 +5933,7 @@
           <t>C | 414呎 (2房)
 $997万
 $24,082/呎
-(22年-09月)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
           <t>A | 465呎 (2房)
 $1073万
 $23,069/呎
-(23年-01月)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -5956,7 +5956,7 @@
           <t>B | 286呎 (1房)
 $738万
 $25,808/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -5964,7 +5964,7 @@
           <t>C | 414呎 (2房)
 $852万
 $20,592/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
           <t>A | 465呎 (2房)
 $968万
 $20,826/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -5987,7 +5987,7 @@
           <t>B | 286呎 (1房)
 $723万
 $25,283/呎
-(21年-08月)</t>
+(21年-08月-23日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -5995,7 +5995,7 @@
           <t>C | 414呎 (2房)
 $971万
 $23,447/呎
-(21年-08月)</t>
+(21年-08月-24日)</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
           <t>B | 286呎 (1房)
 $597万
 $20,885/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -6026,7 +6026,7 @@
           <t>C | 377呎 (2房)
 $1078万
 $28,600/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
